--- a/Codelist Excel Files and Conversion Templates to XML/reinforcementType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/reinforcementType.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for the configuration of steel reinforcement occupying an interval of a rigid inclusion column - rebar cage, single central bar, structural steel section. Distinct from diggs:reinforcementType on diggs:GeosyntheticLayerDesignType (geosynthetic product form) despite the shared element name - a different object, a different vocabulary. Used for the value of diggs:ReinforcementType/diggs:reinforcementType.</t>
+          <t>Codes for the configuration of steel reinforcement occupying an interval of a rigid inclusion column - rebar cage, single central bar, structural steel section. Distinct from diggs:reinforcementType on diggs:DesignGeosyntheticLayerType (geosynthetic product form) despite the shared element name - a different object, a different vocabulary. Used for the value of diggs:ReinforcementType/diggs:reinforcementType.</t>
         </is>
       </c>
     </row>
